--- a/GameConfig/gameAudio.xlsx
+++ b/GameConfig/gameAudio.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -34,10 +34,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>音量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>路径</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -46,14 +42,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>volume</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>loop</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -66,22 +54,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>是否是背景音乐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>isBGM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm_238001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm_238002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>effect_248011</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -89,10 +61,6 @@
     <t>effect_248012</t>
   </si>
   <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>true</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -101,13 +69,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Audio/BGM/BGM_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Audio/BGM/BGM_002</t>
-  </si>
-  <si>
     <t>Audio/Effect/Effect_Cannon_001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -120,10 +81,6 @@
   </si>
   <si>
     <t>effect_248013</t>
-  </si>
-  <si>
-    <t>0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>第一行写字段注释</t>
@@ -165,6 +122,54 @@
   </si>
   <si>
     <t>每一行的作用是固定的不可更改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_238003</t>
+  </si>
+  <si>
+    <t>bgm_238004</t>
+  </si>
+  <si>
+    <t>Audio/BGM/bgm_main</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Audio/BGM/bgm_level_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Audio/BGM/bgm_level_2</t>
+  </si>
+  <si>
+    <t>Audio/BGM/bgm_level_3</t>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐类型. 0-bgm; 1-音效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_238001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_238002</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -747,52 +752,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="25.875" style="12" customWidth="1"/>
-    <col min="3" max="5" width="15.75" style="12" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="13.75" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="2" max="2" width="24.25" style="12" customWidth="1"/>
+    <col min="3" max="3" width="21.375" style="12" customWidth="1"/>
+    <col min="4" max="4" width="15.75" style="12" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="13.75" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
@@ -800,98 +800,108 @@
         <v>1</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="B9" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="C9" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>19</v>
+      <c r="C10" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -912,17 +922,17 @@
   <sheetData>
     <row r="1" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -930,7 +940,7 @@
     </row>
     <row r="5" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/gameAudio.xlsx
+++ b/GameConfig/gameAudio.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -54,33 +54,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>effect_248011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>effect_248012</t>
-  </si>
-  <si>
     <t>true</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>false</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Audio/Effect/Effect_Cannon_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Audio/Effect/Effect_Cannon_002</t>
-  </si>
-  <si>
-    <t>Audio/Effect/Bullet_Explosion_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>effect_248013</t>
   </si>
   <si>
     <t>第一行写字段注释</t>
@@ -170,6 +149,14 @@
   </si>
   <si>
     <t>bgm_238002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Audio/Effect/Bullet_Explosion_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect_248011</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -412,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -449,9 +436,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -752,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.375" style="12" customWidth="1"/>
@@ -772,7 +756,7 @@
         <v>3</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
@@ -786,7 +770,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>5</v>
@@ -800,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>6</v>
@@ -808,100 +792,72 @@
     </row>
     <row r="4" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>28</v>
-      </c>
       <c r="D4" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
         <v>9</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -916,31 +872,31 @@
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultColWidth="89.375" defaultRowHeight="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="89.375" style="18"/>
-    <col min="2" max="16384" width="89.375" style="16"/>
+    <col min="1" max="1" width="89.375" style="17"/>
+    <col min="2" max="16384" width="89.375" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
-        <v>16</v>
+      <c r="A1" s="14" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
-        <v>17</v>
+      <c r="A2" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="19" t="s">
-        <v>18</v>
+      <c r="A3" s="18" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20"/>
+      <c r="A4" s="19"/>
     </row>
     <row r="5" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
-        <v>19</v>
+      <c r="A5" s="16" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
